--- a/backups/lit-review/llm-judge/sources.xlsx
+++ b/backups/lit-review/llm-judge/sources.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/backups/lit-review/llm-judge/sources.xlsx
+++ b/backups/lit-review/llm-judge/sources.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,55 +449,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>doi</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>quotes</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>thoughts</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>drafted</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>flag_note</t>
         </is>
@@ -531,36 +541,39 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2504.12408</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Large Language Models (LLMs) are increasingly used to automate relevance judgments for information retrieval (IR) tasks, often demonstrating agreement with human labels that approaches inter-human agreement. To assess the robustness and reliability of LLM-based relevance judgments, we systematically investigate impact of prompt sensitivity on the task. We collected prompts for relevance assessment from 15 human experts and 15 LLMs across three tasks~ -- ~binary, graded, and pairwise~ -- ~yielding 90 prompts in total. After filtering out unusable prompts from three humans and three LLMs, we employed the remaining 72 prompts with three different LLMs as judges to label document/query pairs from two TREC Deep Learning Datasets (2020 and 2021). We compare LLM-generated labels with TREC official human labels using Cohen's $κ$ and pairwise agreement measures. In addition to investigating the impact of prompt variations on agreement with human labels, we compare human- and LLM-generated prompts and analyze differences among different LLMs as judges. We also compare human- and LLM-generated prompts with the standard UMBRELA prompt used for relevance assessment by Bing and TREC 2024 Retrieval Augmented Generation (RAG) Track. To support future research in LLM-based evaluation, we release all data and prompts at https://github.com/Narabzad/prompt-sensitivity-relevance-judgements/.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>prompt sensitivity, specification choices, judge consistency, llm-based evaluation, human-ai agreement, relevance judgment</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Draft tab — section picker auto-populates from the structured outline; entries shown as Section or Section &gt; Subsection. Word count display: current / target words (where current = total across draft, target from Setup).
-Setup: new "Target word count" integer field
-Setup: new "Formatting guidelines" text area (e.g. for ACL 8-page lim
-aim: To assess the robustness and reliability of LLM-based relevance judgments, we systematically investigate impact of prompt sensitivity on the task.
-methods: We collected prompts for relevance assessment from 15 human experts and 15 LLMs across three tasks—binary, graded, and pairwise—yielding 90 prompts in total.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -590,24 +603,30 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2212.08073</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>As AI systems become more capable, we would like to enlist their help to supervise other AIs. We experiment with methods for training a harmless AI assistant through self-improvement, without any human labels identifying harmful outputs. The only human oversight is provided through a list of rules or principles, and so we refer to the method as 'Constitutional AI'. The process involves both a supervised learning and a reinforcement learning phase. In the supervised phase we sample from an initial model, then generate self-critiques and revisions, and then finetune the original model on revised responses. In the RL phase, we sample from the finetuned model, use a model to evaluate which of the two samples is better, and then train a preference model from this dataset of AI preferences. We then train with RL using the preference model as the reward signal, i.e. we use 'RL from AI Feedback' (RLAIF). As a result we are able to train a harmless but non-evasive AI assistant that engages with harmful queries by explaining its objections to them. Both the SL and RL methods can leverage chain-of-thought style reasoning to improve the human-judged performance and transparency of AI decision making. These methods make it possible to control AI behavior more precisely and with far fewer human labels.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -639,18 +658,24 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>There is an increasing trend towards evaluating NLP models with LLMs instead of human judgments, raising questions about the validity of these evaluations, as well as their reproducibility in the case of proprietary models. We provide JUDGE-BENCH, an extensible collection of 20 NLP datasets with human annotations covering a broad range of evaluated properties and types of data, and comprehensively evaluate 11 current LLMs, covering both open-weight and proprietary models, for their ability to replicate the annotations. Our evaluations show substantial variance across models and datasets. Models are reliable evaluators on some tasks, but overall display substantial variability depending on the property being evaluated, the expertise level of the human judges, and whether the language is human or model-generated. We conclude that LLMs should be carefully validated against human judgments before being used as evaluators.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -682,18 +707,24 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Summary Data analysis workflows in many scientific domains have become increasingly complex and flexible. To assess the impact of this flexibility on functional magnetic resonance imaging (fMRI) results, the same dataset was independently analyzed by 70 teams, testing nine ex-ante hypotheses. The flexibility of analytic approaches is exemplified by the fact that no two teams chose identical workflows to analyze the data. This flexibility resulted in sizeable variation in hypothesis test results, even for teams whose statistical maps were highly correlated at intermediate stages of their analysis pipeline. Variation in reported results was related to several aspects of analysis methodology. Importantly, meta-analytic approaches that aggregated information across teams yielded significant consensus in activated regions across teams. Furthermore, prediction markets of researchers in the field revealed an overestimation of the likelihood of significant findings, even by researchers with direct knowledge of the dataset. Our findings show that analytic flexibility can have substantial effects on scientific conclusions, and demonstrate factors related to variability in fMRI. The results emphasize the importance of validating and sharing complex analysis workflows, and demonstrate the need for multiple analyses of the same data. Potential approaches to mitigate issues related to analytical variability are discussed.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -725,18 +756,24 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ML models often exhibit unexpectedly poor behavior when they are deployed in real-world domains. We identify underspecification as a key reason for these failures. An ML pipeline is underspecified when it can return many predictors with equivalently strong held-out performance in the training domain. Underspecification is common in modern ML pipelines, such as those based on deep learning. Predictors returned by underspecified pipelines are often treated as equivalent based on their training domain performance, but we show here that such predictors can behave very differently in deployment domains. This ambiguity can lead to instability and poor model behavior in practice, and is a distinct failure mode from previously identified issues arising from structural mismatch between training and deployment domains. We show that this problem appears in a wide variety of practical ML pipelines, using examples from computer vision, medical imaging, natural language processing, clinical risk prediction based on electronic health records, and medical genomics. Our results show the need to explicitly account for underspecification in modeling pipelines that are intended for real-world deployment in any domain.</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,18 +805,24 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LLM-based auto-annotators have become a key component of the LLM development process due to their cost-effectiveness and scalability compared to human-based evaluation. However, these auto-annotators can introduce biases that are hard to remove. Even simple, known confounders such as preference for longer outputs remain in existing automated evaluation metrics. We propose a simple regression analysis approach for controlling biases in auto-evaluations. As a real case study, we focus on reducing the length bias of AlpacaEval, a fast and affordable benchmark for instruction-tuned LLMs that uses LLMs to estimate response quality. Despite being highly correlated with human preferences, AlpacaEval is known to favor models that generate longer outputs. We introduce a length-controlled AlpacaEval that aims to answer the counterfactual question: "What would the preference be if the model's and baseline's output had the same length?" To achieve this, we first fit a generalized linear model to predict the biased auto-annotator's preferences based on the mediators we want to control for (length difference) and other relevant features. We then obtain length-controlled preferences by predicting preferences while conditioning the GLM with a zero difference in lengths. Length-controlling not only improves the robustness of the metric to manipulations in model verbosity, but we also find that it increases the Spearman correlation with LMSYS Chatbot Arena from 0.94 to 0.98.</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -811,18 +854,24 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>We introduce Llama Guard, an LLM-based input-output safeguard model geared towards Human-AI conversation use cases. Our model incorporates a safety risk taxonomy, a valuable tool for categorizing a specific set of safety risks found in LLM prompts (i.e., prompt classification). This taxonomy is also instrumental in classifying the responses generated by LLMs to these prompts, a process we refer to as response classification. For the purpose of both prompt and response classification, we have meticulously gathered a dataset of high quality. Llama Guard, a Llama2-7b model that is instruction-tuned on our collected dataset, albeit low in volume, demonstrates strong performance on existing benchmarks such as the OpenAI Moderation Evaluation dataset and ToxicChat, where its performance matches or exceeds that of currently available content moderation tools. Llama Guard functions as a language model, carrying out multi-class classification and generating binary decision scores. Furthermore, the instruction fine-tuning of Llama Guard allows for the customization of tasks and the adaptation of output formats. This feature enhances the model's capabilities, such as enabling the adjustment of taxonomy categories to align with specific use cases, and facilitating zero-shot or few-shot prompting with diverse taxonomies at the input. We are making Llama Guard model weights available and we encourage researchers to further develop and adapt them to meet the evolving needs of the community for AI safety.</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -854,18 +903,24 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>We propose measurement modeling from the quantitative social sciences as a framework for understanding fairness in computational systems. Computational systems often involve unobservable theoretical constructs, such as socioeconomic status, teacher effectiveness, and risk of recidivism. Such constructs cannot be measured directly and must instead be inferred from measurements of observable properties (and other unobservable theoretical constructs) thought to be related to them -- i.e., operationalized via a measurement model. This process, which necessarily involves making assumptions, introduces the potential for mismatches between the theoretical understanding of the construct purported to be measured and its operationalization. We argue that many of the harms discussed in the literature on fairness in computational systems are direct results of such mismatches. We show how some of these harms could have been anticipated and, in some cases, mitigated if viewed through the lens of measurement modeling. To do this, we contribute fairness-oriented conceptualizations of construct reliability and construct validity that unite traditions from political science, education, and psychology and provide a set of tools for making explicit and testing assumptions about constructs and their operationalizations. We then turn to fairness itself, an essentially contested construct that has different theoretical understandings in different contexts. We argue that this contestedness underlies recent debates about fairness definitions: although these debates appear to be about different operationalizations, they are, in fact, debates about different theoretical understandings of fairness. We show how measurement modeling can provide a framework for getting to the core of these debates.</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -897,18 +952,24 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Recently, using a powerful proprietary Large Language Model (LLM) (e.g., GPT-4) as an evaluator for long-form responses has become the de facto standard. However, for practitioners with large-scale evaluation tasks and custom criteria in consideration (e.g., child-readability), using proprietary LLMs as an evaluator is unreliable due to the closed-source nature, uncontrolled versioning, and prohibitive costs. In this work, we propose Prometheus, a fully open-source LLM that is on par with GPT-4's evaluation capabilities when the appropriate reference materials (reference answer, score rubric) are accompanied. We first construct the Feedback Collection, a new dataset that consists of 1K fine-grained score rubrics, 20K instructions, and 100K responses and language feedback generated by GPT-4. Using the Feedback Collection, we train Prometheus, a 13B evaluator LLM that can assess any given long-form text based on customized score rubric provided by the user. Experimental results show that Prometheus scores a Pearson correlation of 0.897 with human evaluators when evaluating with 45 customized score rubrics, which is on par with GPT-4 (0.882), and greatly outperforms ChatGPT (0.392). Furthermore, measuring correlation with GPT-4 with 1222 customized score rubrics across four benchmarks (MT Bench, Vicuna Bench, Feedback Bench, Flask Eval) shows similar trends, bolstering Prometheus's capability as an evaluator LLM. Lastly, Prometheus achieves the highest accuracy on two human preference benchmarks (HHH Alignment &amp;amp; MT Bench Human Judgment) compared to open-sourced reward models explicitly trained on human preference datasets, highlighting its potential as an universal reward model. We open-source our code, dataset, and model at https://kaistai.github.io/prometheus/.</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -940,18 +1001,24 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Evaluation of NLP methods requires testing against a previously vetted gold-standard test set and reporting standard metrics (accuracy/precision/recall/F1). The current assumption is that all items in a given test set are equal with regards to difficulty and discriminating power. We propose Item Response Theory (IRT) from psychometrics as an alternative means for gold-standard test-set generation and NLP system evaluation. IRT is able to describe characteristics of individual items - their difficulty and discriminating power - and can account for these characteristics in its estimation of human intelligence or ability for an NLP task. In this paper, we demonstrate IRT by generating a gold-standard test set for Recognizing Textual Entailment. By collecting a large number of human responses and fitting our IRT model, we show that our IRT model compares NLP systems with the performance in a human population and is able to provide more insight into system performance than standard evaluation metrics. We show that a high accuracy score does not always imply a high IRT score, which depends on the item characteristics and the response pattern.</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -987,14 +1054,16 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1026,18 +1095,24 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Reinforcement learning from human feedback (RLHF) has proven effective in aligning large language models (LLMs) with human preferences, but gathering high-quality preference labels is expensive. RL from AI Feedback (RLAIF), introduced in Bai et al., offers a promising alternative that trains the reward model (RM) on preferences generated by an off-the-shelf LLM. Across the tasks of summarization, helpful dialogue generation, and harmless dialogue generation, we show that RLAIF achieves comparable performance to RLHF. Furthermore, we take a step towards "self-improvement" by demonstrating that RLAIF can outperform a supervised fine-tuned baseline even when the AI labeler is the same size as the policy, or even the exact same checkpoint as the initial policy. Finally, we introduce direct-RLAIF (d-RLAIF) - a technique that circumvents RM training by obtaining rewards directly from an off-the-shelf LLM during RL, which achieves superior performance to canonical RLAIF. Our results suggest that RLAIF can achieve performance on-par with using human feedback, offering a potential solution to the scalability limitations of RLHF.</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1069,18 +1144,24 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Existing LLM-as-a-Judge approaches for evaluating text generation suffer from rating inconsistencies, with low agreement and high rating variance across different evaluator models. We attribute this to subjective evaluation criteria combined with Likert scale scoring in existing protocols. To address this issue, we introduce CheckEval, a checklist-based evaluation framework that improves rating reliability via decomposed binary questions. Through experiments with 12 evaluator models across multiple datasets, we first demonstrate that CheckEval strongly correlates with human judgments. More importantly, CheckEval dramatically improves the average agreement across evaluator models by 0.45 and reduces the score variance. CheckEval scores furthermore have the benefit of being more interpretable because it decomposes evaluation criteria into traceable binary decisions, allowing analyses of specific attributes driving quality judgments.</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1112,18 +1193,24 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>The rapid evolution of Large Language Models (LLMs) has outpaced the development of model evaluation, highlighting the need for continuous curation of new, challenging benchmarks. However, manual curation of high-quality, human-aligned benchmarks is expensive and time-consuming. To address this, we introduce BenchBuilder, an automated pipeline that leverages LLMs to curate high-quality, open-ended prompts from large, crowd-sourced datasets, enabling continuous benchmark updates without human in the loop. We apply BenchBuilder to datasets such as Chatbot Arena and WildChat-1M, extracting challenging prompts and utilizing LLM-as-a-Judge for automatic model evaluation. To validate benchmark quality, we propose new metrics to measure a benchmark's alignment with human preferences and ability to separate models. We release Arena-Hard-Auto, a benchmark consisting 500 challenging prompts curated by BenchBuilder. Arena-Hard-Auto provides 3x higher separation of model performances compared to MT-Bench and achieves 98.6% correlation with human preference rankings, all at a cost of $20. Our work sets a new framework for the scalable curation of automated benchmarks from extensive data.</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1155,18 +1242,24 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Assessment and evaluation have long been critical challenges in artificial intelligence (AI) and natural language processing (NLP). Traditional methods, usually matching-based or small model-based, often fall short in open-ended and dynamic scenarios. Recent advancements in Large Language Models (LLMs) inspire the "LLM-as-a-judge" paradigm, where LLMs are leveraged to perform scoring, ranking, or selection for various machine learning evaluation scenarios. This paper presents a comprehensive survey of LLM-based judgment and assessment, offering an in-depth overview to review this evolving field. We first provide the definition from both input and output perspectives. Then we introduce a systematic taxonomy to explore LLM-as-a-judge along three dimensions: what to judge, how to judge, and how to benchmark. Finally, we also highlight key challenges and promising future directions for this emerging area. More resources on LLM-as-a-judge are on the website: https://llm-as-a-judge.github.io and https://github.com/llm-as-a-judge/Awesome-LLM-as-a-judge.</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1198,18 +1291,24 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Language models (LMs) are becoming the foundation for almost all major language technologies, but their capabilities, limitations, and risks are not well understood. We present Holistic Evaluation of Language Models (HELM) to improve the transparency of language models. First, we taxonomize the vast space of potential scenarios (i.e. use cases) and metrics (i.e. desiderata) that are of interest for LMs. Then we select a broad subset based on coverage and feasibility, noting what's missing or underrepresented (e.g. question answering for neglected English dialects, metrics for trustworthiness). Second, we adopt a multi-metric approach: We measure 7 metrics (accuracy, calibration, robustness, fairness, bias, toxicity, and efficiency) for each of 16 core scenarios when possible (87.5% of the time). This ensures metrics beyond accuracy don't fall to the wayside, and that trade-offs are clearly exposed. We also perform 7 targeted evaluations, based on 26 targeted scenarios, to analyze specific aspects (e.g. reasoning, disinformation). Third, we conduct a large-scale evaluation of 30 prominent language models (spanning open, limited-access, and closed models) on all 42 scenarios, 21 of which were not previously used in mainstream LM evaluation. Prior to HELM, models on average were evaluated on just 17.9% of the core HELM scenarios, with some prominent models not sharing a single scenario in common. We improve this to 96.0%: now all 30 models have been densely benchmarked on the same core scenarios and metrics under standardized conditions. Our evaluation surfaces 25 top-level findings. For full transparency, we release all raw model prompts and completions publicly for further analysis, as well as a general modular toolkit. We intend for HELM to be a living benchmark for the community, continuously updated with new scenarios, metrics, and models.</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1241,18 +1340,24 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>We introduce WildBench, an automated evaluation framework designed to benchmark large language models (LLMs) using challenging, real-world user queries. WildBench consists of 1,024 tasks carefully selected from over one million human-chatbot conversation logs. For automated evaluation with WildBench, we have developed two metrics, WB-Reward and WB-Score, which are computable using advanced LLMs such as GPT-4-turbo. WildBench evaluation uses task-specific checklists to evaluate model outputs systematically and provides structured explanations that justify the scores and comparisons, resulting in more reliable and interpretable automatic judgments. WB-Reward employs fine-grained pairwise comparisons between model responses, generating five potential outcomes: much better, slightly better, slightly worse, much worse, or a tie. Unlike previous evaluations that employed a single baseline model, we selected three baseline models at varying performance levels to ensure a comprehensive pairwise evaluation. Additionally, we propose a simple method to mitigate length bias, by converting outcomes of ``slightly better/worse'' to ``tie'' if the winner response exceeds the loser one by more than $K$ characters. WB-Score evaluates the quality of model outputs individually, making it a fast and cost-efficient evaluation metric. WildBench results demonstrate a strong correlation with the human-voted Elo ratings from Chatbot Arena on hard tasks. Specifically, WB-Reward achieves a Pearson correlation of 0.98 with top-ranking models. Additionally, WB-Score reaches 0.95, surpassing both ArenaHard's 0.91 and AlpacaEval2.0's 0.89 for length-controlled win rates, as well as the 0.87 for regular win rates.</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1284,18 +1389,24 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Prediction problems often admit competing models that perform almost equally well. This effect challenges key assumptions in machine learning when competing models assign conflicting predictions. In this paper, we define predictive multiplicity as the ability of a prediction problem to admit competing models with conflicting predictions. We introduce formal measures to evaluate the severity of predictive multiplicity and develop integer programming tools to compute them exactly for linear classification problems. We apply our tools to measure predictive multiplicity in recidivism prediction problems. Our results show that real-world datasets may admit competing models that assign wildly conflicting predictions, and motivate the need to measure and report predictive multiplicity in model development.</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1327,18 +1438,24 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Trained machine learning models are increasingly used to perform high-impact tasks in areas such as law enforcement, medicine, education, and employment. In order to clarify the intended use cases of machine learning models and minimize their usage in contexts for which they are not well suited, we recommend that released models be accompanied by documentation detailing their performance characteristics. In this paper, we propose a framework that we call model cards, to encourage such transparent model reporting. Model cards are short documents accompanying trained machine learning models that provide benchmarked evaluation in a variety of conditions, such as across different cultural, demographic, or phenotypic groups (e.g., race, geographic location, sex, Fitzpatrick skin type) and intersectional groups (e.g., age and race, or sex and Fitzpatrick skin type) that are relevant to the intended application domains. Model cards also disclose the context in which models are intended to be used, details of the performance evaluation procedures, and other relevant information. While we focus primarily on human-centered machine learning models in the application fields of computer vision and natural language processing, this framework can be used to document any trained machine learning model. To solidify the concept, we provide cards for two supervised models: One trained to detect smiling faces in images, and one trained to detect toxic comments in text. We propose model cards as a step towards the responsible democratization of machine learning and related AI technology, increasing transparency into how well AI technology works. We hope this work encourages those releasing trained machine learning models to accompany model releases with similar detailed evaluation numbers and other relevant documentation.</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1370,18 +1487,24 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Abstract Recent advances in LLMs have led to an abundance of evaluation benchmarks, which typically rely on a single instruction template per task. We create a large-scale collection of instruction paraphrases and comprehensively analyze the brittleness introduced by single-prompt evaluations across 6.5M instances, involving 20 different LLMs and 39 tasks from 3 benchmarks. We find that different instruction templates lead to very different performance, both absolute and relative. Instead, we propose a set of diverse metrics on multiple instruction paraphrases, specifically tailored for different use cases (e.g., LLM vs. downstream development), ensuring a more reliable and meaningful assessment of LLM capabilities. We show that our metrics provide new insights into the strengths and limitations of current LLMs.</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1417,14 +1540,16 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1456,18 +1581,24 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>The Rashomon Effect, coined by Leo Breiman, describes the phenomenon that there exist many equally good predictive models for the same dataset. This phenomenon happens for many real datasets and when it does, it sparks both magic and consternation, but mostly magic. In light of the Rashomon Effect, this perspective piece proposes reshaping the way we think about machine learning, particularly for tabular data problems in the nondeterministic (noisy) setting. We address how the Rashomon Effect impacts (1) the existence of simple-yet-accurate models, (2) flexibility to address user preferences, such as fairness and monotonicity, without losing performance, (3) uncertainty in predictions, fairness, and explanations, (4) reliable variable importance, (5) algorithm choice, specifically, providing advanced knowledge of which algorithms might be suitable for a given problem, and (6) public policy. We also discuss a theory of when the Rashomon Effect occurs and why. Our goal is to illustrate how the Rashomon Effect can have a massive impact on the use of machine learning for complex problems in society.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1499,18 +1630,24 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>In recent years, Large Language Models (LLMs) have witnessed a remarkable surge in prevalence, altering the landscape of natural language processing and machine learning. One key factor in improving the performance of LLMs is alignment with humans achieved with Reinforcement Learning from Human Feedback (RLHF), as for many LLMs such as GPT-4, Bard, etc. In addition, recent studies are investigating the replacement of human feedback with feedback from other LLMs named Reinforcement Learning from AI Feedback (RLAIF). We examine the biases that come along with evaluating LLMs with other LLMs and take a closer look into verbosity bias -- a bias where LLMs sometimes prefer more verbose answers even if they have similar qualities. We see that in our problem setting, GPT-4 prefers longer answers more than humans. We also propose a metric to measure this bias.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1542,18 +1679,24 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Large Language Models (LLMs) are regularly being used to label data across many domains and for myriad tasks. By simply asking the LLM for an answer, or ``prompting,'' practitioners are able to use LLMs to quickly get a response for an arbitrary task. This prompting is done through a series of decisions by the practitioner, from simple wording of the prompt, to requesting the output in a certain data format, to jailbreaking in the case of prompts that address more sensitive topics. In this work, we ask: do variations in the way a prompt is constructed change the ultimate decision of the LLM? We answer this using a series of prompt variations across a variety of text classification tasks. We find that even the smallest of perturbations, such as adding a space at the end of a prompt, can cause the LLM to change its answer. Further, we find that requesting responses in XML and commonly used jailbreaks can have cataclysmic effects on the data labeled by LLMs.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1585,18 +1728,24 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>As large language models (LLMs) are adopted as a fundamental component of language technologies, it is crucial to accurately characterize their performance. Because choices in prompt design can strongly influence model behavior, this design process is critical in effectively using any modern pre-trained generative language model. In this work, we focus on LLM sensitivity to a quintessential class of meaning-preserving design choices: prompt formatting. We find that several widely used open-source LLMs are extremely sensitive to subtle changes in prompt formatting in few-shot settings, with performance differences of up to 76 accuracy points when evaluated using LLaMA-2-13B. Sensitivity remains even when increasing model size, the number of few-shot examples, or performing instruction tuning. Our analysis suggests that work evaluating LLMs with prompting-based methods would benefit from reporting a range of performance across plausible prompt formats, instead of the currently-standard practice of reporting performance on a single format. We also show that format performance only weakly correlates between models, which puts into question the methodological validity of comparing models with an arbitrarily chosen, fixed prompt format. To facilitate systematic analysis we propose FormatSpread, an algorithm that rapidly evaluates a sampled set of plausible prompt formats for a given task, and reports the interval of expected performance without accessing model weights. Furthermore, we present a suite of analyses that characterize the nature of this sensitivity, including exploring the influence of particular atomic perturbations and the internal representation of particular formats.</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1628,18 +1777,24 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>It is almost always easier to find an accurate-but-complex model than an accurate-yet-simple model. Finding optimal, sparse, accurate models of various forms (linear models with integer coefficients, decision sets, rule lists, decision trees) is generally NP-hard. We often do not know whether the search for a simpler model will be worthwhile, and thus we do not go to the trouble of searching for one. In this work, we ask an important practical question: can accurate-yet-simple models be proven to exist, or shown likely to exist, before explicitly searching for them? We hypothesize that there is an important reason that simple-yet-accurate models often do exist. This hypothesis is that the size of the Rashomon set is often large, where the Rashomon set is the set of almost-equally-accurate models from a function class. If the Rashomon set is large, it contains numerous accurate models, and perhaps at least one of them is the simple model we desire. In this work, we formally present the Rashomon ratio as a new gauge of simplicity for a learning problem, depending on a function class and a data set. The Rashomon ratio is the ratio of the volume of the set of accurate models to the volume of the hypothesis space, and it is different from standard complexity measures from statistical learning theory. Insight from studying the Rashomon ratio provides an easy way to check whether a simpler model might exist for a problem before finding it, namely whether several different machine learning methods achieve similar performance on the data. In that sense, the Rashomon ratio is a powerful tool for understanding why and when an accurate-yet-simple model might exist. If, as we hypothesize in this work, many real-world data sets admit large Rashomon sets, the implications are vast: it means that simple or interpretable models may often be used for high-stakes decisions without losing accuracy.</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1671,18 +1826,24 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>LLM-as-a-judge has become a promising paradigm for using large language models (LLMs) to evaluate natural language generation (NLG), but the uncertainty of its evaluation remains underexplored. This lack of reliability may limit its deployment in many applications. This work presents the first framework to analyze the uncertainty by offering a prediction interval of LLM-based scoring via conformal prediction. Conformal prediction constructs continuous prediction intervals from a single evaluation run, and we design an ordinal boundary adjustment for discrete rating tasks. We also suggest a midpoint-based score within the interval as a low-bias alternative to raw model score and weighted average. We perform extensive experiments and analysis, which show that conformal prediction can provide valid prediction interval with coverage guarantees. We also explore the usefulness of interval midpoint and judge reprompting for better judgment.</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1714,18 +1875,24 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Twenty-nine teams involving 61 analysts used the same data set to address the same research question: whether soccer referees are more likely to give red cards to dark-skin-toned players than to light-skin-toned players. Analytic approaches varied widely across the teams, and the estimated effect sizes ranged from 0.89 to 2.93 ( Mdn = 1.31) in odds-ratio units. Twenty teams (69%) found a statistically significant positive effect, and 9 teams (31%) did not observe a significant relationship. Overall, the 29 different analyses used 21 unique combinations of covariates. Neither analysts’ prior beliefs about the effect of interest nor their level of expertise readily explained the variation in the outcomes of the analyses. Peer ratings of the quality of the analyses also did not account for the variability. These findings suggest that significant variation in the results of analyses of complex data may be difficult to avoid, even by experts with honest intentions. Crowdsourcing data analysis, a strategy in which numerous research teams are recruited to simultaneously investigate the same research question, makes transparent how defensible, yet subjective, analytic choices influence research results.</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1761,14 +1928,16 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1800,18 +1969,24 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Empirical research inevitably includes constructing a data set by processing raw data into a form ready for statistical analysis. Data processing often involves choices among several reasonable options for excluding, transforming, and coding data. We suggest that instead of performing only one analysis, researchers could perform a multiverse analysis, which involves performing all analyses across the whole set of alternatively processed data sets corresponding to a large set of reasonable scenarios. Using an example focusing on the effect of fertility on religiosity and political attitudes, we show that analyzing a single data set can be misleading and propose a multiverse analysis as an alternative practice. A multiverse analysis offers an idea of how much the conclusions change because of arbitrary choices in data construction and gives pointers as to which choices are most consequential in the fragility of the result.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1843,18 +2018,24 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Recent years have seen numerous NLP datasets introduced to evaluate the performance of fine-tuned models on natural language understanding tasks. Recent results from large pretrained models, though, show that many of these datasets are largely saturated and unlikely to be able to detect further progress. What kind of datasets are still effective at discriminating among strong models, and what kind of datasets should we expect to be able to detect future improvements? To measure this uniformly across datasets, we draw on Item Response Theory and evaluate 29 datasets using predictions from 18 pretrained Transformer models on individual test examples. We find that Quoref, HellaSwag, and MC-TACO are best suited for distinguishing among state-of-the-art models, while SNLI, MNLI, and CommitmentBank seem to be saturated for current strong models. We also observe span selection task format, which is used for QA datasets like QAMR or SQuAD2.0, is effective in differentiating between strong and weak models.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1886,18 +2067,24 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>In this paper, we uncover a systematic bias in the evaluation paradigm of adopting large language models~(LLMs), e.g., GPT-4, as a referee to score and compare the quality of responses generated by candidate models. We find that the quality ranking of candidate responses can be easily hacked by simply altering their order of appearance in the context. This manipulation allows us to skew the evaluation result, making one model appear considerably superior to the other, e.g., Vicuna-13B could beat ChatGPT on 66 over 80 tested queries with ChatGPT as an evaluator. To address this issue, we propose a calibration framework with three simple yet effective strategies: 1) Multiple Evidence Calibration, which requires the evaluator model to generate multiple evaluation evidence before assigning ratings; 2) Balanced Position Calibration, which aggregates results across various orders to determine the final score; 3) Human-in-the-Loop Calibration, which introduces a balanced position diversity entropy to measure the difficulty of each example and seeks human assistance when needed. We also manually annotate the "win/tie/lose" outcomes of responses from ChatGPT and Vicuna-13B in the Vicuna Benchmark's question prompt, and extensive experiments demonstrate that our approach successfully mitigates evaluation bias, resulting in closer alignment with human judgments. We release our code and human annotation at \url{https://github.com/i-Eval/FairEval} to facilitate future research.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1929,18 +2116,24 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Evaluating large language model (LLM) based chat assistants is challenging due to their broad capabilities and the inadequacy of existing benchmarks in measuring human preferences. To address this, we explore using strong LLMs as judges to evaluate these models on more open-ended questions. We examine the usage and limitations of LLM-as-a-judge, including position, verbosity, and self-enhancement biases, as well as limited reasoning ability, and propose solutions to mitigate some of them. We then verify the agreement between LLM judges and human preferences by introducing two benchmarks: MT-bench, a multi-turn question set; and Chatbot Arena, a crowdsourced battle platform. Our results reveal that strong LLM judges like GPT-4 can match both controlled and crowdsourced human preferences well, achieving over 80% agreement, the same level of agreement between humans. Hence, LLM-as-a-judge is a scalable and explainable way to approximate human preferences, which are otherwise very expensive to obtain. Additionally, we show our benchmark and traditional benchmarks complement each other by evaluating several variants of LLaMA and Vicuna. The MT-bench questions, 3K expert votes, and 30K conversations with human preferences are publicly available at https://github.com/lm-sys/FastChat/tree/main/fastchat/llm_judge.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1972,18 +2165,24 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Large Language Models (LLMs) have unlocked new capabilities and applications; however, evaluating the alignment with human preferences still poses significant challenges. To address this issue, we introduce Chatbot Arena, an open platform for evaluating LLMs based on human preferences. Our methodology employs a pairwise comparison approach and leverages input from a diverse user base through crowdsourcing. The platform has been operational for several months, amassing over 240K votes. This paper describes the platform, analyzes the data we have collected so far, and explains the tried-and-true statistical methods we are using for efficient and accurate evaluation and ranking of models. We confirm that the crowdsourced questions are sufficiently diverse and discriminating and that the crowdsourced human votes are in good agreement with those of expert raters. These analyses collectively establish a robust foundation for the credibility of Chatbot Arena. Because of its unique value and openness, Chatbot Arena has emerged as one of the most referenced LLM leaderboards, widely cited by leading LLM developers and companies. Our demo is publicly available at \url{https://chat.lmsys.org}.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2019,14 +2218,16 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2062,14 +2263,16 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2105,14 +2308,16 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backups/lit-review/llm-judge/sources.xlsx
+++ b/backups/lit-review/llm-judge/sources.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,7 +559,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
+          <t>
 </t>
         </is>
       </c>
